--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLUB BALONCESTO SAN FERNANDO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLUB BALONCESTO SAN FERNANDO.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>89.68039999999999</v>
+        <v>82.87</v>
       </c>
       <c r="E2" t="n">
-        <v>61.2371</v>
+        <v>59.9812</v>
       </c>
       <c r="F2" t="n">
-        <v>28.4433</v>
+        <v>22.8891</v>
       </c>
       <c r="G2" t="n">
         <v>41.0181</v>
@@ -610,13 +610,13 @@
         <v>43.3571</v>
       </c>
       <c r="S2" t="n">
-        <v>12.5278</v>
+        <v>5.7175</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3072</v>
+        <v>0.05149999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>11.2203</v>
+        <v>5.6662</v>
       </c>
       <c r="V2" t="n">
         <v>29.8348</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>49.3391</v>
+        <v>29.0626</v>
       </c>
       <c r="E3" t="n">
-        <v>39.1122</v>
+        <v>26.2458</v>
       </c>
       <c r="F3" t="n">
-        <v>10.227</v>
+        <v>2.8164</v>
       </c>
       <c r="G3" t="n">
         <v>-13.0668</v>
@@ -688,13 +688,13 @@
         <v>34.834</v>
       </c>
       <c r="S3" t="n">
-        <v>36.1074</v>
+        <v>15.8307</v>
       </c>
       <c r="T3" t="n">
-        <v>20.6617</v>
+        <v>7.7957</v>
       </c>
       <c r="U3" t="n">
-        <v>15.4458</v>
+        <v>8.035399999999999</v>
       </c>
       <c r="V3" t="n">
         <v>38.898</v>
@@ -721,13 +721,13 @@
         <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>22.7896</v>
+        <v>23.0728</v>
       </c>
       <c r="E4" t="n">
-        <v>12.8081</v>
+        <v>12.1281</v>
       </c>
       <c r="F4" t="n">
-        <v>9.9815</v>
+        <v>10.9447</v>
       </c>
       <c r="G4" t="n">
         <v>6.288</v>
@@ -766,13 +766,13 @@
         <v>32.0547</v>
       </c>
       <c r="S4" t="n">
-        <v>1.402100000000001</v>
+        <v>1.6855</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6331</v>
+        <v>0.9531999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.231</v>
+        <v>0.7322</v>
       </c>
       <c r="V4" t="n">
         <v>1.5737</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. REMESAL LEÓN</t>
+          <t>M. TRILLO MANGANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>14.3385</v>
+        <v>16.7742</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3385</v>
+        <v>2.1939</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>14.5804</v>
       </c>
       <c r="G5" t="n">
-        <v>14.3385</v>
+        <v>11.525</v>
       </c>
       <c r="H5" t="n">
-        <v>9.984</v>
+        <v>5.794700000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3546</v>
+        <v>5.730099999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>14.3385</v>
+        <v>11.5888</v>
       </c>
       <c r="K5" t="n">
-        <v>9.984</v>
+        <v>7.9732</v>
       </c>
       <c r="L5" t="n">
-        <v>4.3546</v>
+        <v>3.6153</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.06380000000000033</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-2.1783</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.1146</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>12.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-8.523199999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>21.4931</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1.1768</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.8704999999999998</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.306</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-6.543799999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.001199999999999979</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-6.5427</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. TRILLO MANGANO</t>
+          <t>J. REMESAL LEÓN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>9.2372</v>
+        <v>14.3385</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6368999999999998</v>
+        <v>14.3385</v>
       </c>
       <c r="F6" t="n">
-        <v>9.8748</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>11.525</v>
+        <v>14.3385</v>
       </c>
       <c r="H6" t="n">
-        <v>5.794700000000001</v>
+        <v>9.984</v>
       </c>
       <c r="I6" t="n">
-        <v>5.730099999999999</v>
+        <v>4.3546</v>
       </c>
       <c r="J6" t="n">
-        <v>11.5888</v>
+        <v>14.3385</v>
       </c>
       <c r="K6" t="n">
-        <v>7.9732</v>
+        <v>9.984</v>
       </c>
       <c r="L6" t="n">
-        <v>3.6153</v>
+        <v>4.3546</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06380000000000033</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1783</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.1146</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>12.97</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-8.523199999999999</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>21.4931</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-8.713900000000001</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.7017</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.012</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-6.543799999999999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001199999999999979</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.5427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ESCAMILLA DE SANTOS</t>
+          <t>J. RODRIGUEZ -  GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>9.163499999999999</v>
+        <v>9.1417</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2423</v>
+        <v>9.1417</v>
       </c>
       <c r="F7" t="n">
-        <v>4.9213</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>9.0337</v>
+        <v>9.1417</v>
       </c>
       <c r="H7" t="n">
-        <v>12.6654</v>
+        <v>3.5431</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.6312</v>
+        <v>5.5988</v>
       </c>
       <c r="J7" t="n">
-        <v>20.6617</v>
+        <v>9.1417</v>
       </c>
       <c r="K7" t="n">
-        <v>20.5796</v>
+        <v>3.5431</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08219999999999961</v>
+        <v>5.5988</v>
       </c>
       <c r="M7" t="n">
-        <v>-11.6282</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.9144</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.714</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.408800000000001</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-35.0193</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>32.6105</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5529</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>5.3849</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8322000000000002</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.0142</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>13.2146</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-15.2288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ -  GUERRA SALGUEIRO</t>
+          <t>I. GARCÍA REYES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,34 +1030,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>9.1417</v>
+        <v>6.0309</v>
       </c>
       <c r="E8" t="n">
-        <v>9.1417</v>
+        <v>6.0309</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>9.1417</v>
+        <v>6.0309</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5431</v>
+        <v>3.5428</v>
       </c>
       <c r="I8" t="n">
-        <v>5.5988</v>
+        <v>2.4884</v>
       </c>
       <c r="J8" t="n">
-        <v>9.1417</v>
+        <v>6.0309</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5431</v>
+        <v>3.5428</v>
       </c>
       <c r="L8" t="n">
-        <v>5.5988</v>
+        <v>2.4884</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. GARCÍA REYES</t>
+          <t>D. ESCAMILLA DE SANTOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>6.0309</v>
+        <v>5.049899999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0309</v>
+        <v>-1.3139</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>6.363999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>6.0309</v>
+        <v>9.0337</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5428</v>
+        <v>12.6654</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4884</v>
+        <v>-3.6312</v>
       </c>
       <c r="J9" t="n">
-        <v>6.0309</v>
+        <v>20.6617</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5428</v>
+        <v>20.5796</v>
       </c>
       <c r="L9" t="n">
-        <v>2.4884</v>
+        <v>0.08219999999999961</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-11.6282</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-7.9144</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-3.714</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-2.408800000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-35.0193</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>32.6105</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.4390999999999998</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.1711</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.6102000000000002</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.0142</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>13.2146</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-15.2288</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. GALAN PLAZA</t>
+          <t>C. GALÁN PLAZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>4.4469</v>
+        <v>3.1546</v>
       </c>
       <c r="E10" t="n">
-        <v>12.0657</v>
+        <v>3.1546</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.6189</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1187</v>
+        <v>3.1546</v>
       </c>
       <c r="H10" t="n">
-        <v>4.024100000000001</v>
+        <v>1.2883</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.1427</v>
+        <v>1.8663</v>
       </c>
       <c r="J10" t="n">
-        <v>12.3098</v>
+        <v>3.1546</v>
       </c>
       <c r="K10" t="n">
-        <v>12.081</v>
+        <v>1.2883</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2285999999999999</v>
+        <v>1.8663</v>
       </c>
       <c r="M10" t="n">
-        <v>-15.4283</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.0572</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-7.3714</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5557999999999996</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-18.1581</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>18.7141</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>6.3197</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>6.5909</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2708000000000003</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6896999999999998</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>11.3229</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.6333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. GALÁN PLAZA</t>
+          <t>C. GALAN PLAZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>3.1546</v>
+        <v>3.0661</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1546</v>
+        <v>9.5222</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-6.4564</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1546</v>
+        <v>-3.1187</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2883</v>
+        <v>4.024100000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8663</v>
+        <v>-7.1427</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1546</v>
+        <v>12.3098</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2883</v>
+        <v>12.081</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8663</v>
+        <v>0.2285999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-15.4283</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-8.0572</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-7.3714</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.5557999999999996</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-18.1581</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>18.7141</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.9391</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.0477</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.8914000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.6896999999999998</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>11.3229</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-10.6333</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.002800000000001</v>
+        <v>0.5469000000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3599</v>
+        <v>8.132</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.3628</v>
+        <v>-7.5848</v>
       </c>
       <c r="G12" t="n">
         <v>-6.2998</v>
@@ -1390,13 +1390,13 @@
         <v>31.3135</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.238099999999999</v>
+        <v>0.3115000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.8953</v>
+        <v>-0.1231</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.343</v>
+        <v>0.4348999999999996</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3206000000000007</v>
@@ -1423,13 +1423,13 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.5235</v>
+        <v>-4.694699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.9148</v>
+        <v>-9.7559</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3912</v>
+        <v>5.0614</v>
       </c>
       <c r="G13" t="n">
         <v>2.7621</v>
@@ -1468,13 +1468,13 @@
         <v>16.8611</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.2485</v>
+        <v>-0.4198</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.5507</v>
+        <v>-2.3917</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3022000000000001</v>
+        <v>1.9721</v>
       </c>
       <c r="V13" t="n">
         <v>-3.1461</v>
@@ -1501,13 +1501,13 @@
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.2009</v>
+        <v>-10.3138</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.766</v>
+        <v>-6.7592</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.434700000000001</v>
+        <v>-3.554799999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-9.624700000000001</v>
@@ -1546,13 +1546,13 @@
         <v>28.7194</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8037</v>
+        <v>3.6907</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.5205</v>
+        <v>0.4865</v>
       </c>
       <c r="U14" t="n">
-        <v>4.3241</v>
+        <v>3.2042</v>
       </c>
       <c r="V14" t="n">
         <v>13.7782</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>I. GARCIA REYES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.4658</v>
+        <v>-14.5653</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.8324</v>
+        <v>-19.5099</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.6334</v>
+        <v>4.9444</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.3527</v>
+        <v>-14.7858</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4328</v>
+        <v>-5.2438</v>
       </c>
       <c r="I15" t="n">
-        <v>-7.920299999999999</v>
+        <v>-9.541500000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2817</v>
+        <v>-12.1337</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3516</v>
+        <v>-3.3355</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.0698</v>
+        <v>-8.798299999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-10.6347</v>
+        <v>-2.6518</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.7844</v>
+        <v>-1.9087</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.850499999999999</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1502</v>
+        <v>4.8176</v>
       </c>
       <c r="Q15" t="n">
-        <v>-14.267</v>
+        <v>-10.7465</v>
       </c>
       <c r="R15" t="n">
-        <v>17.4171</v>
+        <v>15.5642</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3242</v>
+        <v>-1.6397</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3209</v>
+        <v>0.5406999999999998</v>
       </c>
       <c r="U15" t="n">
-        <v>2.0032</v>
+        <v>-2.1802</v>
       </c>
       <c r="V15" t="n">
-        <v>-12.587</v>
+        <v>-2.9578</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8321</v>
+        <v>2.83</v>
       </c>
       <c r="X15" t="n">
-        <v>-15.4192</v>
+        <v>-5.7876</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>-18.3684</v>
+        <v>-15.581</v>
       </c>
       <c r="E16" t="n">
-        <v>-15.8498</v>
+        <v>-13.9979</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5186</v>
+        <v>-1.5828</v>
       </c>
       <c r="G16" t="n">
         <v>-8.886800000000001</v>
@@ -1702,13 +1702,13 @@
         <v>9.2645</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6707</v>
+        <v>1.1172</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.8489</v>
+        <v>0.003000000000000114</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1784</v>
+        <v>1.1142</v>
       </c>
       <c r="V16" t="n">
         <v>-4.846299999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. GARCIA REYES</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>-21.5464</v>
+        <v>-16.7608</v>
       </c>
       <c r="E17" t="n">
-        <v>-22.9399</v>
+        <v>-10.31</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3938</v>
+        <v>-6.4509</v>
       </c>
       <c r="G17" t="n">
-        <v>-14.7858</v>
+        <v>-9.3527</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.2438</v>
+        <v>-1.4328</v>
       </c>
       <c r="I17" t="n">
-        <v>-9.541500000000001</v>
+        <v>-7.920299999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>-12.1337</v>
+        <v>1.2817</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.3355</v>
+        <v>3.3516</v>
       </c>
       <c r="L17" t="n">
-        <v>-8.798299999999999</v>
+        <v>-2.0698</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6518</v>
+        <v>-10.6347</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9087</v>
+        <v>-4.7844</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-5.850499999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>4.8176</v>
+        <v>3.1502</v>
       </c>
       <c r="Q17" t="n">
-        <v>-10.7465</v>
+        <v>-14.267</v>
       </c>
       <c r="R17" t="n">
-        <v>15.5642</v>
+        <v>17.4171</v>
       </c>
       <c r="S17" t="n">
-        <v>-8.620799999999999</v>
+        <v>2.0289</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.8895</v>
+        <v>-0.1568</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.7309</v>
+        <v>2.1859</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.9578</v>
+        <v>-12.587</v>
       </c>
       <c r="W17" t="n">
-        <v>2.83</v>
+        <v>2.8321</v>
       </c>
       <c r="X17" t="n">
-        <v>-5.7876</v>
+        <v>-15.4192</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CASTRO DIANEZ</t>
+          <t>M. CABEZA RUEDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>-27.3009</v>
+        <v>-19.6837</v>
       </c>
       <c r="E18" t="n">
-        <v>-24.5101</v>
+        <v>-15.2192</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7906</v>
+        <v>-4.4648</v>
       </c>
       <c r="G18" t="n">
-        <v>-11.3825</v>
+        <v>8.150099999999998</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7037000000000004</v>
+        <v>-0.355</v>
       </c>
       <c r="I18" t="n">
-        <v>-10.679</v>
+        <v>8.5053</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2646</v>
+        <v>29.5018</v>
       </c>
       <c r="K18" t="n">
-        <v>5.995200000000001</v>
+        <v>13.7275</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.730800000000001</v>
+        <v>15.7741</v>
       </c>
       <c r="M18" t="n">
-        <v>-13.6475</v>
+        <v>-21.3516</v>
       </c>
       <c r="N18" t="n">
-        <v>-6.6989</v>
+        <v>-14.0829</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.9483</v>
+        <v>-7.2687</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.2262</v>
+        <v>-15.7495</v>
       </c>
       <c r="Q18" t="n">
-        <v>-29.2752</v>
+        <v>-55.5859</v>
       </c>
       <c r="R18" t="n">
-        <v>22.0492</v>
+        <v>39.8368</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.620900000000001</v>
+        <v>-4.212999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.162</v>
+        <v>-4.2341</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.4588</v>
+        <v>0.02070000000000011</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0708</v>
+        <v>-7.8714</v>
       </c>
       <c r="W18" t="n">
-        <v>5.6628</v>
+        <v>15.0992</v>
       </c>
       <c r="X18" t="n">
-        <v>-6.7336</v>
+        <v>-22.9706</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CABEZA RUEDA</t>
+          <t>D. CASTRO DIANEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>-33.1464</v>
+        <v>-20.9533</v>
       </c>
       <c r="E19" t="n">
-        <v>-24.3207</v>
+        <v>-20.9819</v>
       </c>
       <c r="F19" t="n">
-        <v>-8.825800000000001</v>
+        <v>0.02859999999999996</v>
       </c>
       <c r="G19" t="n">
-        <v>8.150099999999998</v>
+        <v>-11.3825</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.355</v>
+        <v>-0.7037000000000004</v>
       </c>
       <c r="I19" t="n">
-        <v>8.5053</v>
+        <v>-10.679</v>
       </c>
       <c r="J19" t="n">
-        <v>29.5018</v>
+        <v>2.2646</v>
       </c>
       <c r="K19" t="n">
-        <v>13.7275</v>
+        <v>5.995200000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>15.7741</v>
+        <v>-3.730800000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-21.3516</v>
+        <v>-13.6475</v>
       </c>
       <c r="N19" t="n">
-        <v>-14.0829</v>
+        <v>-6.6989</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.2687</v>
+        <v>-6.9483</v>
       </c>
       <c r="P19" t="n">
-        <v>-15.7495</v>
+        <v>-7.2262</v>
       </c>
       <c r="Q19" t="n">
-        <v>-55.5859</v>
+        <v>-29.2752</v>
       </c>
       <c r="R19" t="n">
-        <v>39.8368</v>
+        <v>22.0492</v>
       </c>
       <c r="S19" t="n">
-        <v>-17.6758</v>
+        <v>-1.2733</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.3349</v>
+        <v>0.3661000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.3405</v>
+        <v>-1.6391</v>
       </c>
       <c r="V19" t="n">
-        <v>-7.8714</v>
+        <v>-1.0708</v>
       </c>
       <c r="W19" t="n">
-        <v>15.0992</v>
+        <v>5.6628</v>
       </c>
       <c r="X19" t="n">
-        <v>-22.9706</v>
+        <v>-6.7336</v>
       </c>
     </row>
     <row r="20">
@@ -1969,16 +1969,16 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>70.76729999999996</v>
+        <v>90.55560000000003</v>
       </c>
       <c r="E20" t="n">
-        <v>43.72039999999997</v>
+        <v>53.021</v>
       </c>
       <c r="F20" t="n">
-        <v>27.04810000000001</v>
+        <v>37.53449999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>34.92489999999999</v>
+        <v>34.9249</v>
       </c>
       <c r="H20" t="n">
         <v>95.2441</v>
@@ -2014,13 +2014,13 @@
         <v>364.0892999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>7.249100000000002</v>
+        <v>27.0376</v>
       </c>
       <c r="T20" t="n">
-        <v>-3.004799999999998</v>
+        <v>6.297099999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>10.2548</v>
+        <v>20.7421</v>
       </c>
       <c r="V20" t="n">
         <v>43.4164</v>
